--- a/assets_management/tests/data/asset_category_depreciation_type.xlsx
+++ b/assets_management/tests/data/asset_category_depreciation_type.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -40,55 +40,82 @@
     <t xml:space="preserve">depreciation_type_id</t>
   </si>
   <si>
-    <t xml:space="preserve">z0bug.depr_type_1</t>
+    <t xml:space="preserve">z0bug.depr_type_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets_management.ad_mode_materiale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.asset_category_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets_management.ad_type_civilistico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets_management.ad_type_fiscale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets_management.ad_type_gestionale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assets_management.ad_mode_immateriale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.asset_category_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_07</t>
   </si>
   <si>
     <t xml:space="preserve">25.0</t>
   </si>
   <si>
-    <t xml:space="preserve">False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets_management.ad_mode_materiale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.asset_category_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets_management.ad_type_civilistico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.depr_type_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets_management.ad_type_fiscale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.depr_type_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets_management.ad_type_gestionale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.depr_type_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">True</t>
-  </si>
-  <si>
-    <t xml:space="preserve">assets_management.ad_mode_immateriale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.asset_category_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.depr_type_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.depr_type_6</t>
+    <t xml:space="preserve">z0bug.asset_category_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.asset_category_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.depr_type_12</t>
   </si>
 </sst>
 </file>
@@ -164,7 +191,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -174,6 +201,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -300,7 +331,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.89"/>
@@ -452,6 +483,126 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
